--- a/mapping/SB_DWH/Mapping_DIM_LOS_WORKSTEP.xlsx
+++ b/mapping/SB_DWH/Mapping_DIM_LOS_WORKSTEP.xlsx
@@ -877,7 +877,11 @@
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr"/>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Hệ nguồn</t>
+        </is>
+      </c>
       <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="17" t="inlineStr">
         <is>
@@ -997,7 +1001,11 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr"/>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Ngày bắt đầu hiệu lực</t>
+        </is>
+      </c>
       <c r="D13" s="17" t="inlineStr"/>
       <c r="E13" s="17" t="inlineStr">
         <is>
@@ -1021,7 +1029,11 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Ngày hết hiệu lực</t>
+        </is>
+      </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
           <t>NULL = bản ghi hiện hành</t>
@@ -1118,7 +1130,6 @@
     <row r="68" ht="17" customHeight="1"/>
     <row r="69" ht="16" customHeight="1"/>
     <row r="70" ht="17" customHeight="1"/>
-    <row r="72"/>
   </sheetData>
   <autoFilter ref="A5:E70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
